--- a/outputs/B_bank_errors.xlsx
+++ b/outputs/B_bank_errors.xlsx
@@ -12,13 +12,23 @@
     <sheet name="Page Audit" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Read me" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cell Evidence" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Verification" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Repair Proposals" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Correction History" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$F$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Repair Proposals'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,9 +36,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -79,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -97,6 +108,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -955,6 +969,201 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F20"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C1" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E1" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId120"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Time UTC</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Previous hash</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Event hash</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1166,7 +1375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1263,7 +1472,7 @@
         <v>0.98</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -1283,96 +1492,12 @@
         <v>4</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>673.6</v>
+        <v>1694.126</v>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>native</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>668.4</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>digital</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>native</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>words</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>666.4</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1831,10 +1956,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1869,7 +1994,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.162</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
@@ -1932,8 +2057,6105 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Cell evidence</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Repair proposals</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Arithmetic-derived suggestions only. Source documents may contain errors. Never applied automatically.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B8"/>
+  <autoFilter ref="A1:B10"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M121"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Source page</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>x0</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>y0</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>y1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>OCR score</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Initial reading</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>header</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>header</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>header</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>header</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>header</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>header</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>TX-001</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Entry 1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1040.00</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>TX-002</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Entry 2</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1028.00</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>TX-003</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Entry 3</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1015.00</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>TX-004</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Entry 4</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>43.00</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>1058.00</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>TX-005</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Entry 5</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>1043.00</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>TX-006</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Entry 6</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>16.00</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>1027.00</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>TX-007</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Entry 7</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>46.00</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>1073.00</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>TX-008</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Entry 8</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>1055.00</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>TX-009</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n"/>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Entry 9</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>1036.00</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>TX-010</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Entry 10</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n"/>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>49.00</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>1085.00</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n"/>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>TX-011</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n"/>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Entry 11</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n"/>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n"/>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>1081.00</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>TX-012</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="17" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n"/>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n"/>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Entry 12</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n"/>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="17" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="17" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>416</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n"/>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>1042.00</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="17" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n"/>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>TX-013</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n"/>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n"/>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Entry 13</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n"/>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>52.00</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>443</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n"/>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>1094.00</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="17" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>TX-014</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="17" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n"/>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="17" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n"/>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Entry 14</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="17" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n"/>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>24.00</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="17" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n"/>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="17" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n"/>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>1070.00</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="17" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n"/>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>TX-015</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="17" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n"/>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="17" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n"/>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Entry 15</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="17" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n"/>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="17" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n"/>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="17" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>497</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n"/>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>1045.00</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="17" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n"/>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>TX-016</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="17" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n"/>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="17" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n"/>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Entry 16</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="17" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n"/>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="17" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n"/>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="17" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n"/>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>1100.00</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="17" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n"/>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>TX-017</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="17" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n"/>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="17" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n"/>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Entry 17</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="17" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n"/>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>27.00</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="17" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n"/>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="17" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>551</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n"/>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>1073.00</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="17" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n"/>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>TX-018</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="17" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n"/>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="17" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n"/>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Entry 18</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="17" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n"/>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="17" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n"/>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="17" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n"/>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>1045.00</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="17" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>632</v>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="17" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>632</v>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n"/>
+      <c r="K117" s="2" t="inlineStr"/>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="17" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>632</v>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n"/>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="17" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>545</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>632</v>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n"/>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>249.00</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="17" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>685</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>632</v>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n"/>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="17" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>605</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>632</v>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>native-lines</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="n"/>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M121"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source SHA-256</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>0312be673c7db85435e2a34ddcb8c6b2b688c9e0f5825b2702d47b02188ed142</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Extraction snapshot SHA-256</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>ae35bfb77cf38f71a1eb6c4dfa0a1c239d4e90859ef2c1add8c15041d08f2d94</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Review status</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Unreviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Review meaning</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>A human source-check attestation; not independent accuracy certification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Review note</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>cells</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>cells with source boxes</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>equations</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>equation checks</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>failed equation checks</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>proposals with multiple equations</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="64" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Inferred relation</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Checked rows</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Matching rows</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Empirical agreement</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Violations</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Previous Z - X + Y = Z</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Inferred from this document; not a probability of correctness.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Supporting equations</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1081.00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1064.00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row11; T1:balance:C6-C4+C5@row12</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1085.00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1102.00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row11</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row11</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row11</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row12</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-17.00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row12</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1042.00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1059.00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row12</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/B_bank_errors.xlsx
+++ b/outputs/B_bank_errors.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$2</definedName>
@@ -1472,7 +1472,7 @@
         <v>0.98</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.055</v>
+        <v>0.079</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1994,95 +1994,131 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
+        <v>0.133</v>
+      </c>
+    </row>
+    <row r="4" ht="119" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Yellow cells</t>
+          <t>Text encoding</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Review required. See Validation Report for the reason and source row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
+          <t>All XLSX string fields use a reversible encoding: a literal backslash is doubled; XML-forbidden code points use a backslash followed by u and four hexadecimal digits. An underscore starting an OOXML escape-like sequence uses the same Unicode encoding. Decode left to right, treating each doubled backslash as one literal backslash. The full audit JSON and saved workspace retain the original strings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="68" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Source row</t>
+          <t>Long text</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Data row within the extracted source table, excluding detected headers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
+          <t>Values exceeding Excel's 32767-character cell limit show an explicit preview. The Long Text sheet preserves the complete encoded value in numbered chunks. Join its chunks in order before decoding the text encoding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="68" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Confidence</t>
+          <t>Small numbers</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Extraction heuristic / OCR score, not a calibrated probability of correctness.</t>
+          <t>Numbers below Excel's normal floating-point range remain exact text. Numbers needing more than 12 decimal places use General formatting; percentages needing more than 12 display decimals remain text, avoiding a false zero.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>Yellow cells</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ISO and unambiguous day-first dates are typed. Ambiguous dates stay text.</t>
+          <t>Review required. See Validation Report for the reason and source row.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Source row</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Source strings are stored as text. No source formulas are executed.</t>
+          <t>Data row within the extracted source table, excluding detected headers.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Cell evidence</t>
+          <t>Confidence</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+          <t>Extraction heuristic / OCR score, not a calibrated probability of correctness.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>ISO and unambiguous day-first dates are typed. Ambiguous dates stay text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Source strings are stored as text. No source formulas are executed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Cell evidence</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Repair proposals</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Arithmetic-derived suggestions only. Source documents may contain errors. Never applied automatically.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7613,7 +7649,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ae35bfb77cf38f71a1eb6c4dfa0a1c239d4e90859ef2c1add8c15041d08f2d94</t>
+          <t>6f5d7309f2e36332cb200ec40feaed5ca2270b2a1ffa116fbf5bdb69476159a2</t>
         </is>
       </c>
     </row>

--- a/outputs/B_bank_errors.xlsx
+++ b/outputs/B_bank_errors.xlsx
@@ -10,25 +10,27 @@
     <sheet name="Data 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Validation Report" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Page Audit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Read me" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cell Evidence" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Verification" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Repair Proposals" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Correction History" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Join Receipt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Read me" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cell Evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Verification" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Constraints" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Repair Proposals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Correction History" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$F$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Repair Proposals'!$A$1:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$M$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1101,6 +1103,352 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Supporting equations</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1081.00</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1064.00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row11; T1:balance:C6-C4+C5@row12</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1085.00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1102.00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row11</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row11</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17.00</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row11</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39.00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row12</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-17.00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row12</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1042.00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1059.00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>T1:balance:C6-C4+C5@row12</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>proposal_only</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Inferred document arithmetic; verify the source before applying.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1472,7 +1820,7 @@
         <v>0.98</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.079</v>
+        <v>0.382</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -1503,6 +1851,103 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source pages</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Page joins</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Repeated headers removed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Split rows recovered</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PDF page</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source rows on page</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Output rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1950,7 +2395,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1994,7 +2439,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.133</v>
+        <v>0.5649999999999999</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -2123,7 +2568,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7604,7 +8049,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7649,7 +8094,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>6f5d7309f2e36332cb200ec40feaed5ca2270b2a1ffa116fbf5bdb69476159a2</t>
+          <t>b51002132c517c47568cd3604426fbd78bd34784e544f7d2a31304f0fe1819ba</t>
         </is>
       </c>
     </row>
@@ -7751,7 +8196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7848,350 +8293,4 @@
   <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="54" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="65" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Excel row</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Supporting equations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>1081.00</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>1064.00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>T1:balance:C6-C4+C5@row11; T1:balance:C6-C4+C5@row12</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>proposal_only</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Inferred document arithmetic; verify the source before applying.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>1085.00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>1102.00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>T1:balance:C6-C4+C5@row11</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>proposal_only</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Inferred document arithmetic; verify the source before applying.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>T1:balance:C6-C4+C5@row11</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>proposal_only</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Inferred document arithmetic; verify the source before applying.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17.00</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>T1:balance:C6-C4+C5@row11</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>proposal_only</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Inferred document arithmetic; verify the source before applying.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>22.00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>39.00</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>T1:balance:C6-C4+C5@row12</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>proposal_only</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Inferred document arithmetic; verify the source before applying.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-17.00</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>T1:balance:C6-C4+C5@row12</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>proposal_only</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Inferred document arithmetic; verify the source before applying.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1042.00</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1059.00</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>T1:balance:C6-C4+C5@row12</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>proposal_only</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Inferred document arithmetic; verify the source before applying.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I8"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/B_bank_errors.xlsx
+++ b/outputs/B_bank_errors.xlsx
@@ -26,8 +26,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$M$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$O$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
@@ -1086,12 +1086,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId116"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1820,7 +1816,7 @@
         <v>0.98</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.382</v>
+        <v>0.138</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -2439,7 +2435,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.303</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -2574,7 +2570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2590,6 +2586,8 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2658,6 +2656,16 @@
           <t>Role</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Location status</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Location reason</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -2703,6 +2711,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -2748,6 +2766,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -2793,6 +2821,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -2838,6 +2876,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -2883,6 +2931,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -2928,6 +2986,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -2973,6 +3041,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -3018,6 +3096,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -3063,6 +3151,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -3108,6 +3206,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -3153,6 +3261,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -3198,6 +3316,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -3243,6 +3371,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -3288,6 +3426,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -3333,6 +3481,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -3378,6 +3536,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -3423,6 +3591,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -3468,6 +3646,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -3513,6 +3701,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -3558,6 +3756,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -3603,6 +3811,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -3648,6 +3866,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -3693,6 +3921,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -3738,6 +3976,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -3783,6 +4031,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -3828,6 +4086,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -3873,6 +4141,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -3918,6 +4196,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -3963,6 +4251,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -4008,6 +4306,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -4053,6 +4361,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -4098,6 +4416,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -4143,6 +4471,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -4188,6 +4526,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -4233,6 +4581,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -4278,6 +4636,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -4323,6 +4691,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -4368,6 +4746,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -4413,6 +4801,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -4458,6 +4856,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -4503,6 +4911,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -4548,6 +4966,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -4593,6 +5021,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -4638,6 +5076,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -4683,6 +5131,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -4728,6 +5186,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -4773,6 +5241,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
@@ -4818,6 +5296,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -4863,6 +5351,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -4908,6 +5406,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -4953,6 +5461,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="17" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
@@ -4998,6 +5516,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -5043,6 +5571,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="17" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
@@ -5088,6 +5626,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="17" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -5133,6 +5681,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="17" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
@@ -5178,6 +5736,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -5223,6 +5791,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="17" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -5268,6 +5846,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="17" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -5313,6 +5901,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="17" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -5358,6 +5956,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="17" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -5403,6 +6011,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="17" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
@@ -5448,6 +6066,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -5493,6 +6121,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="17" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
@@ -5538,6 +6176,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="17" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -5583,6 +6231,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="17" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
@@ -5628,6 +6286,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -5673,6 +6341,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="17" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
@@ -5718,6 +6396,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="17" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -5763,6 +6451,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="17" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
@@ -5808,6 +6506,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="17" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -5853,6 +6561,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="17" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
@@ -5898,6 +6616,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="17" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -5943,6 +6671,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="17" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
@@ -5988,6 +6726,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="17" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -6033,6 +6781,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="17" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
@@ -6078,6 +6836,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="17" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -6123,6 +6891,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="17" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
@@ -6168,6 +6946,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="17" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -6213,6 +7001,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="17" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
@@ -6258,6 +7056,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="17" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -6303,6 +7111,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="17" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
@@ -6348,6 +7166,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="17" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -6393,6 +7221,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="17" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
@@ -6438,6 +7276,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="17" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -6483,6 +7331,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="17" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
@@ -6528,6 +7386,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -6573,6 +7441,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="17" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
@@ -6618,6 +7496,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -6663,6 +7551,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="17" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
@@ -6708,6 +7606,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="17" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -6753,6 +7661,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="17" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
@@ -6798,6 +7716,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="17" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -6843,6 +7771,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="17" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
@@ -6888,6 +7826,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="17" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -6933,6 +7881,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="17" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
@@ -6978,6 +7936,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="17" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -7023,6 +7991,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="17" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
@@ -7068,6 +8046,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="17" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -7113,6 +8101,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="17" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
@@ -7158,6 +8156,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="17" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
@@ -7203,6 +8211,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="17" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
@@ -7248,6 +8266,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="17" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
@@ -7293,6 +8321,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="17" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
@@ -7338,6 +8376,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="17" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
@@ -7383,6 +8431,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="17" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
@@ -7428,6 +8486,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="17" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -7473,6 +8541,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="17" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
@@ -7518,6 +8596,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="17" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
@@ -7563,6 +8651,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="17" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
@@ -7608,6 +8706,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="17" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
@@ -7653,6 +8761,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="17" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
@@ -7698,6 +8816,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="17" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -7743,6 +8871,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="17" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
@@ -7786,6 +8924,16 @@
       <c r="M115" s="2" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -7829,6 +8977,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>The extracted cell is empty; no source location is required.</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="17" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
@@ -7870,6 +9028,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>The extracted cell is empty; no source location is required.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="17" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -7915,6 +9083,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="17" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
@@ -7958,6 +9136,16 @@
       <c r="M119" s="2" t="inlineStr">
         <is>
           <t>extracted</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
     </row>
@@ -8001,6 +9189,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>The extracted cell is empty; no source location is required.</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="17" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
@@ -8042,9 +9240,19 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>The extracted cell is empty; no source location is required.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M121"/>
+  <autoFilter ref="A1:O121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8055,10 +9263,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -8094,7 +9302,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>b51002132c517c47568cd3604426fbd78bd34784e544f7d2a31304f0fe1819ba</t>
+          <t>57646dd054cc1fc85cd6496f20fe76f0248b3d3435364b7553104a94069dee00</t>
         </is>
       </c>
     </row>
@@ -8133,65 +9341,117 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>cells</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>114</v>
+          <t>Export type</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Draft Excel</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>cells with source boxes</t>
+          <t>Non-empty exported cells</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>equations</t>
+          <t>Cells with source boxes</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>equation checks</t>
+          <t>Cells requiring full-page evidence review</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>failed equation checks</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>2</v>
+          <t>Cell source-box coverage</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>cells</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>cells with source boxes</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>equations</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>equation checks</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>failed equation checks</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>proposals with multiple equations</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
